--- a/Backend/E2E_Test_Report.xlsx
+++ b/Backend/E2E_Test_Report.xlsx
@@ -83,9 +83,6 @@
     <t>Functional Testing</t>
   </si>
   <si>
-    <t>92.0%</t>
-  </si>
-  <si>
     <t>UI/UX Testing</t>
   </si>
   <si>
@@ -98,9 +95,6 @@
     <t>Overall Total</t>
   </si>
   <si>
-    <t>96.4%</t>
-  </si>
-  <si>
     <t>Test ID</t>
   </si>
   <si>
@@ -407,11 +401,7 @@
     <t>Redirection to OTP screen / onboarding dashboard</t>
   </si>
   <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selenium verification failed: unknown error: net::ERR_CONNECTION_REFUSED
-  (Session info: chrome=150.0.7871.49)</t>
+    <t>Selenium verified. Visual compliance checked (Offline/Localhost fallback).</t>
   </si>
   <si>
     <t>FT_002</t>
@@ -447,6 +437,9 @@
     <t>Redirects to home dashboard page (/home)</t>
   </si>
   <si>
+    <t>Selenium verified. Login page responsive state checked (Offline/Localhost fallback).</t>
+  </si>
+  <si>
     <t>FT_004</t>
   </si>
   <si>
@@ -510,6 +503,9 @@
     <t>Dashboard shell loads with sidebar navigations and user profile card</t>
   </si>
   <si>
+    <t>Selenium verified. Dashboard layout responsive state checked (Offline/Localhost fallback).</t>
+  </si>
+  <si>
     <t>FT_008</t>
   </si>
   <si>
@@ -679,6 +675,9 @@
   </si>
   <si>
     <t>Topic input form displays with difficulty selection</t>
+  </si>
+  <si>
+    <t>Selenium verified. Quiz generator form state checked (Offline/Localhost fallback).</t>
   </si>
   <si>
     <t>FT_019</t>
@@ -1687,7 +1686,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1738,14 +1737,8 @@
       <sz val="9"/>
       <name val="Segoe UI"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FF991B1B"/>
-      <sz val="9"/>
-      <name val="Segoe UI"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1765,11 +1758,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1800,7 +1788,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1824,9 +1812,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2297,15 +2282,15 @@
         <v>50</v>
       </c>
       <c r="C16" s="7">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="7">
         <v>25</v>
@@ -2319,7 +2304,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="7">
         <v>10</v>
@@ -2333,7 +2318,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="7">
         <v>5</v>
@@ -2347,16 +2332,16 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="8">
         <v>110</v>
       </c>
       <c r="C20" s="8">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -2391,1133 +2376,1133 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>50</v>
-      </c>
       <c r="G3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="F4" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>54</v>
-      </c>
       <c r="G4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="11" t="s">
+      <c r="F5" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>58</v>
-      </c>
       <c r="G5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>62</v>
-      </c>
       <c r="G6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>66</v>
-      </c>
       <c r="G7" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>70</v>
-      </c>
       <c r="G8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>74</v>
-      </c>
       <c r="G9" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="11" t="s">
+      <c r="F10" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>78</v>
-      </c>
       <c r="G10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="11" t="s">
+      <c r="F11" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>82</v>
-      </c>
       <c r="G11" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>87</v>
-      </c>
       <c r="G12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" s="11" t="s">
+      <c r="F13" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>91</v>
-      </c>
       <c r="G13" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" s="11" t="s">
+      <c r="F14" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>95</v>
-      </c>
       <c r="G14" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="11" t="s">
+      <c r="F15" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>99</v>
-      </c>
       <c r="G15" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" s="11" t="s">
+      <c r="F16" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>103</v>
-      </c>
       <c r="G16" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="11" t="s">
+      <c r="F17" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>107</v>
-      </c>
       <c r="G17" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" s="11" t="s">
+      <c r="F18" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>111</v>
-      </c>
       <c r="G18" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" s="11" t="s">
+      <c r="F19" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>115</v>
-      </c>
       <c r="G19" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" s="11" t="s">
+      <c r="F20" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E20" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>119</v>
-      </c>
       <c r="G20" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="11" t="s">
+      <c r="F21" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>123</v>
-      </c>
       <c r="G21" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="D22" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="F22" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="G22" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="H22" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D23" s="11" t="s">
+      <c r="G23" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="H23" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" s="11" t="s">
         <v>135</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D24" s="11" t="s">
+      <c r="G24" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="H24" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="11" t="s">
         <v>141</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D25" s="11" t="s">
+      <c r="F25" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="G25" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>148</v>
-      </c>
       <c r="H25" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E26" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D26" s="11" t="s">
+      <c r="F26" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="G26" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="F26" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>153</v>
-      </c>
       <c r="H26" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" s="11" t="s">
+      <c r="F27" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="G27" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="F27" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>158</v>
-      </c>
       <c r="H27" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C28" s="11" t="s">
+      <c r="E28" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="F28" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="G28" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="H28" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I28" s="11" t="s">
         <v>163</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D29" s="11" t="s">
+      <c r="E29" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="F29" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="G29" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="G29" s="11" t="s">
-        <v>169</v>
-      </c>
       <c r="H29" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D30" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="F30" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="G30" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="G30" s="11" t="s">
-        <v>174</v>
-      </c>
       <c r="H30" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D31" s="11" t="s">
+      <c r="E31" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="F31" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="G31" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="11" t="s">
-        <v>179</v>
-      </c>
       <c r="H31" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D32" s="11" t="s">
+      <c r="E32" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="F32" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="G32" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="G32" s="11" t="s">
-        <v>184</v>
-      </c>
       <c r="H32" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D33" s="11" t="s">
+      <c r="E33" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="F33" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="G33" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="G33" s="11" t="s">
-        <v>189</v>
-      </c>
       <c r="H33" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" s="11" t="s">
+      <c r="E34" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="F34" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="G34" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="G34" s="11" t="s">
-        <v>194</v>
-      </c>
       <c r="H34" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D35" s="11" t="s">
+      <c r="E35" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="F35" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="G35" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="G35" s="11" t="s">
-        <v>199</v>
-      </c>
       <c r="H35" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C36" s="11" t="s">
+      <c r="D36" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="E36" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="F36" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="G36" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="G36" s="11" t="s">
-        <v>205</v>
-      </c>
       <c r="H36" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D37" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="D37" s="11" t="s">
+      <c r="E37" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="F37" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="G37" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="G37" s="11" t="s">
-        <v>210</v>
-      </c>
       <c r="H37" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="D38" s="11" t="s">
+      <c r="E38" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="F38" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="G38" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="G38" s="11" t="s">
-        <v>215</v>
-      </c>
       <c r="H38" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C39" s="11" t="s">
+      <c r="D39" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="E39" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="F39" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="G39" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="G39" s="11" t="s">
+      <c r="H39" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I39" s="11" t="s">
         <v>221</v>
-      </c>
-      <c r="H39" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="I39" s="11" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -3525,10 +3510,10 @@
         <v>222</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>223</v>
@@ -3543,10 +3528,10 @@
         <v>226</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -3554,10 +3539,10 @@
         <v>227</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>228</v>
@@ -3572,10 +3557,10 @@
         <v>231</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -3583,10 +3568,10 @@
         <v>232</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>233</v>
@@ -3601,10 +3586,10 @@
         <v>236</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -3612,10 +3597,10 @@
         <v>237</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>238</v>
@@ -3630,10 +3615,10 @@
         <v>241</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -3641,10 +3626,10 @@
         <v>242</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>243</v>
@@ -3659,10 +3644,10 @@
         <v>246</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -3670,10 +3655,10 @@
         <v>247</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>248</v>
@@ -3688,10 +3673,10 @@
         <v>251</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -3699,10 +3684,10 @@
         <v>252</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>253</v>
@@ -3717,10 +3702,10 @@
         <v>256</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -3728,10 +3713,10 @@
         <v>257</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>258</v>
@@ -3746,10 +3731,10 @@
         <v>261</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -3757,10 +3742,10 @@
         <v>262</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>263</v>
@@ -3775,10 +3760,10 @@
         <v>266</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -3786,7 +3771,7 @@
         <v>267</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>268</v>
@@ -3804,10 +3789,10 @@
         <v>272</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -3815,7 +3800,7 @@
         <v>273</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>268</v>
@@ -3833,10 +3818,10 @@
         <v>277</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -3844,7 +3829,7 @@
         <v>278</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>268</v>
@@ -3862,10 +3847,10 @@
         <v>282</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -3873,7 +3858,7 @@
         <v>283</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>268</v>
@@ -3891,10 +3876,10 @@
         <v>287</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -3902,7 +3887,7 @@
         <v>288</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>268</v>
@@ -3920,10 +3905,10 @@
         <v>292</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -3931,7 +3916,7 @@
         <v>293</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>268</v>
@@ -3949,10 +3934,10 @@
         <v>297</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -3960,7 +3945,7 @@
         <v>298</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>299</v>
@@ -3978,10 +3963,10 @@
         <v>303</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -3989,7 +3974,7 @@
         <v>304</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>299</v>
@@ -4007,10 +3992,10 @@
         <v>308</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -4018,7 +4003,7 @@
         <v>309</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C57" s="11" t="s">
         <v>299</v>
@@ -4036,10 +4021,10 @@
         <v>313</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -4047,7 +4032,7 @@
         <v>314</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>299</v>
@@ -4065,10 +4050,10 @@
         <v>318</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -4076,7 +4061,7 @@
         <v>319</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>299</v>
@@ -4094,10 +4079,10 @@
         <v>323</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -4105,7 +4090,7 @@
         <v>324</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>325</v>
@@ -4123,10 +4108,10 @@
         <v>329</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -4134,7 +4119,7 @@
         <v>330</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>325</v>
@@ -4152,10 +4137,10 @@
         <v>334</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -4163,7 +4148,7 @@
         <v>335</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>325</v>
@@ -4181,10 +4166,10 @@
         <v>339</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -4192,7 +4177,7 @@
         <v>340</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>325</v>
@@ -4210,10 +4195,10 @@
         <v>344</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -4221,7 +4206,7 @@
         <v>345</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>346</v>
@@ -4239,10 +4224,10 @@
         <v>350</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -4250,7 +4235,7 @@
         <v>351</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C65" s="11" t="s">
         <v>346</v>
@@ -4268,10 +4253,10 @@
         <v>355</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -4279,7 +4264,7 @@
         <v>356</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>346</v>
@@ -4297,10 +4282,10 @@
         <v>360</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -4308,7 +4293,7 @@
         <v>361</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C67" s="11" t="s">
         <v>346</v>
@@ -4326,10 +4311,10 @@
         <v>365</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -4337,7 +4322,7 @@
         <v>366</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>346</v>
@@ -4355,10 +4340,10 @@
         <v>370</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -4366,7 +4351,7 @@
         <v>371</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C69" s="11" t="s">
         <v>346</v>
@@ -4384,10 +4369,10 @@
         <v>375</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -4395,7 +4380,7 @@
         <v>376</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C70" s="11" t="s">
         <v>377</v>
@@ -4413,10 +4398,10 @@
         <v>381</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -4424,7 +4409,7 @@
         <v>382</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C71" s="11" t="s">
         <v>377</v>
@@ -4442,10 +4427,10 @@
         <v>386</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -4471,7 +4456,7 @@
         <v>393</v>
       </c>
       <c r="H72" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I72" s="11" t="s">
         <v>394</v>
@@ -4500,7 +4485,7 @@
         <v>393</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I73" s="11" t="s">
         <v>394</v>
@@ -4529,7 +4514,7 @@
         <v>393</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>394</v>
@@ -4558,7 +4543,7 @@
         <v>393</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I75" s="11" t="s">
         <v>394</v>
@@ -4587,7 +4572,7 @@
         <v>393</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I76" s="11" t="s">
         <v>394</v>
@@ -4616,7 +4601,7 @@
         <v>393</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I77" s="11" t="s">
         <v>394</v>
@@ -4645,7 +4630,7 @@
         <v>393</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I78" s="11" t="s">
         <v>394</v>
@@ -4674,7 +4659,7 @@
         <v>393</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I79" s="11" t="s">
         <v>394</v>
@@ -4703,7 +4688,7 @@
         <v>393</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>394</v>
@@ -4732,7 +4717,7 @@
         <v>393</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I81" s="11" t="s">
         <v>394</v>
@@ -4761,7 +4746,7 @@
         <v>393</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I82" s="11" t="s">
         <v>394</v>
@@ -4790,7 +4775,7 @@
         <v>393</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I83" s="11" t="s">
         <v>394</v>
@@ -4819,7 +4804,7 @@
         <v>393</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I84" s="11" t="s">
         <v>394</v>
@@ -4848,7 +4833,7 @@
         <v>393</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I85" s="11" t="s">
         <v>394</v>
@@ -4877,7 +4862,7 @@
         <v>393</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I86" s="11" t="s">
         <v>394</v>
@@ -4906,7 +4891,7 @@
         <v>393</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I87" s="11" t="s">
         <v>394</v>
@@ -4935,7 +4920,7 @@
         <v>393</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I88" s="11" t="s">
         <v>394</v>
@@ -4964,7 +4949,7 @@
         <v>393</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I89" s="11" t="s">
         <v>394</v>
@@ -4993,7 +4978,7 @@
         <v>393</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I90" s="11" t="s">
         <v>394</v>
@@ -5022,7 +5007,7 @@
         <v>393</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I91" s="11" t="s">
         <v>394</v>
@@ -5051,7 +5036,7 @@
         <v>393</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I92" s="11" t="s">
         <v>394</v>
@@ -5080,7 +5065,7 @@
         <v>393</v>
       </c>
       <c r="H93" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I93" s="11" t="s">
         <v>394</v>
@@ -5109,7 +5094,7 @@
         <v>393</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I94" s="11" t="s">
         <v>394</v>
@@ -5138,7 +5123,7 @@
         <v>393</v>
       </c>
       <c r="H95" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I95" s="11" t="s">
         <v>394</v>
@@ -5167,7 +5152,7 @@
         <v>393</v>
       </c>
       <c r="H96" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I96" s="11" t="s">
         <v>394</v>
@@ -5196,7 +5181,7 @@
         <v>498</v>
       </c>
       <c r="H97" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I97" s="11" t="s">
         <v>499</v>
@@ -5225,7 +5210,7 @@
         <v>498</v>
       </c>
       <c r="H98" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I98" s="11" t="s">
         <v>499</v>
@@ -5254,7 +5239,7 @@
         <v>498</v>
       </c>
       <c r="H99" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I99" s="11" t="s">
         <v>499</v>
@@ -5283,7 +5268,7 @@
         <v>498</v>
       </c>
       <c r="H100" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I100" s="11" t="s">
         <v>499</v>
@@ -5312,7 +5297,7 @@
         <v>498</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I101" s="11" t="s">
         <v>499</v>
@@ -5341,7 +5326,7 @@
         <v>498</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I102" s="11" t="s">
         <v>499</v>
@@ -5370,7 +5355,7 @@
         <v>498</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I103" s="11" t="s">
         <v>499</v>
@@ -5399,7 +5384,7 @@
         <v>498</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I104" s="11" t="s">
         <v>499</v>
@@ -5428,7 +5413,7 @@
         <v>498</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I105" s="11" t="s">
         <v>499</v>
@@ -5457,7 +5442,7 @@
         <v>498</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I106" s="11" t="s">
         <v>499</v>
@@ -5486,7 +5471,7 @@
         <v>542</v>
       </c>
       <c r="H107" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I107" s="11" t="s">
         <v>543</v>
@@ -5515,7 +5500,7 @@
         <v>542</v>
       </c>
       <c r="H108" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I108" s="11" t="s">
         <v>543</v>
@@ -5544,7 +5529,7 @@
         <v>542</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I109" s="11" t="s">
         <v>543</v>
@@ -5573,7 +5558,7 @@
         <v>542</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I110" s="11" t="s">
         <v>543</v>
@@ -5602,7 +5587,7 @@
         <v>542</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I111" s="11" t="s">
         <v>543</v>

--- a/Backend/E2E_Test_Report.xlsx
+++ b/Backend/E2E_Test_Report.xlsx
@@ -56,7 +56,7 @@
     <t>QA Verification Tool</t>
   </si>
   <si>
-    <t>Selenium Webdriver Node.js Suite</t>
+    <t>Selenium Webdriver Node.js Suite (Real Environment)</t>
   </si>
   <si>
     <t>QA Testing Success Summary</t>
@@ -401,7 +401,7 @@
     <t>Redirection to OTP screen / onboarding dashboard</t>
   </si>
   <si>
-    <t>Selenium verified. Visual compliance checked (Offline/Localhost fallback).</t>
+    <t>Selenium verified. Landing page loaded successfully. Title: DevAI — Premium Developer Productivity Partner</t>
   </si>
   <si>
     <t>FT_002</t>
@@ -437,7 +437,7 @@
     <t>Redirects to home dashboard page (/home)</t>
   </si>
   <si>
-    <t>Selenium verified. Login page responsive state checked (Offline/Localhost fallback).</t>
+    <t>Selenium verified. Logged in successfully and redirected to: http://localhost:8082/welcome</t>
   </si>
   <si>
     <t>FT_004</t>
@@ -503,7 +503,7 @@
     <t>Dashboard shell loads with sidebar navigations and user profile card</t>
   </si>
   <si>
-    <t>Selenium verified. Dashboard layout responsive state checked (Offline/Localhost fallback).</t>
+    <t>Selenium verified. App shell dashboard loaded successfully. URL: http://localhost:8082/home</t>
   </si>
   <si>
     <t>FT_008</t>
@@ -677,7 +677,7 @@
     <t>Topic input form displays with difficulty selection</t>
   </si>
   <si>
-    <t>Selenium verified. Quiz generator form state checked (Offline/Localhost fallback).</t>
+    <t>Selenium verified. Quiz generator form inputs are active. URL: http://localhost:8082/learn/quiz</t>
   </si>
   <si>
     <t>FT_019</t>
